--- a/StructureDefinition-mii-pr-mikrobio-antigen-antikoerper-quantitativ.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-antigen-antikoerper-quantitativ.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5874" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5874" uniqueCount="780">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T16:03:21+00:00</t>
+    <t>2026-09-10T13:00:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1346,6 +1346,9 @@
 </t>
   </si>
   <si>
+    <t>In der Serologie ist ein praekoordiniertes Specimen ausdruecklich zulaessig — anders als in den uebrigen Bereichen dieses Moduls gilt die Konvention 'System = XXX' hier NICHT. Das europaeische Whitepaper begruendet die Ausnahme damit, dass in der Serologie nur wenige Materialien vorkommen, ueberwiegend Serum, und ein Code-Wildwuchs deshalb nicht droht.</t>
+  </si>
+  <si>
     <t>LOINC-Code, der den gemessenen Laborparameter bzw. durchgeführten Labortest beschreibt.</t>
   </si>
   <si>
@@ -1871,7 +1874,7 @@
     <t>Observation.value[x].code</t>
   </si>
   <si>
-    <t>Coded form of the unit</t>
+    <t>Bevorzugt eine Einheit mit LITER als Nenner — ng/L, pg/L, ug/L, [IU]/L, [arb'U]/L. Das europaeische Whitepaper empfiehlt fuer die Serologie den Liter, weil das NPU-System ihn durchgaengig verwendet. Die mL-Varianten bleiben zulaessig, weil [IU]/mL international verbreitet ist.</t>
   </si>
   <si>
     <t>A computer processable form of the unit in some unit representation system.</t>
@@ -2118,7 +2121,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-probe)
 </t>
   </si>
   <si>
@@ -9701,16 +9704,16 @@
         <v>282</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>63</v>
+        <v>422</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>76</v>
@@ -9739,7 +9742,7 @@
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>76</v>
@@ -9774,10 +9777,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9874,10 +9877,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9976,10 +9979,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10078,10 +10081,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10178,10 +10181,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10280,10 +10283,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10384,10 +10387,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10486,10 +10489,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10590,10 +10593,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10694,10 +10697,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10798,13 +10801,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>76</v>
@@ -10848,7 +10851,7 @@
         <v>76</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>76</v>
@@ -10866,10 +10869,10 @@
         <v>141</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>76</v>
@@ -10904,10 +10907,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11008,10 +11011,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11034,19 +11037,19 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>76</v>
@@ -11095,7 +11098,7 @@
         <v>76</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>74</v>
@@ -11112,10 +11115,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11212,10 +11215,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11314,10 +11317,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11343,13 +11346,13 @@
         <v>98</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11399,7 +11402,7 @@
         <v>76</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>74</v>
@@ -11408,7 +11411,7 @@
         <v>83</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>91</v>
@@ -11416,10 +11419,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11445,13 +11448,13 @@
         <v>125</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11480,10 +11483,10 @@
         <v>141</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>76</v>
@@ -11501,7 +11504,7 @@
         <v>76</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>74</v>
@@ -11518,10 +11521,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11547,13 +11550,13 @@
         <v>258</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11603,7 +11606,7 @@
         <v>76</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>74</v>
@@ -11620,10 +11623,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11649,13 +11652,13 @@
         <v>98</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11705,7 +11708,7 @@
         <v>76</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>74</v>
@@ -11722,10 +11725,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11748,16 +11751,16 @@
         <v>84</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -11807,7 +11810,7 @@
         <v>76</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>74</v>
@@ -11824,14 +11827,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -11850,19 +11853,19 @@
         <v>84</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>76</v>
@@ -11911,7 +11914,7 @@
         <v>76</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>74</v>
@@ -11928,10 +11931,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12028,10 +12031,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12130,10 +12133,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12159,13 +12162,13 @@
         <v>98</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12215,7 +12218,7 @@
         <v>76</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>74</v>
@@ -12224,7 +12227,7 @@
         <v>83</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>91</v>
@@ -12232,10 +12235,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12261,13 +12264,13 @@
         <v>125</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12296,10 +12299,10 @@
         <v>141</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>76</v>
@@ -12317,7 +12320,7 @@
         <v>76</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>74</v>
@@ -12334,10 +12337,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12363,13 +12366,13 @@
         <v>258</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12419,7 +12422,7 @@
         <v>76</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>74</v>
@@ -12436,10 +12439,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12465,13 +12468,13 @@
         <v>98</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -12521,7 +12524,7 @@
         <v>76</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>74</v>
@@ -12538,14 +12541,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12564,19 +12567,19 @@
         <v>84</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>76</v>
@@ -12625,7 +12628,7 @@
         <v>76</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>74</v>
@@ -12637,15 +12640,15 @@
         <v>90</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12742,10 +12745,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12844,13 +12847,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="B99" t="s" s="2">
-        <v>500</v>
-      </c>
       <c r="C99" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>103</v>
@@ -12872,13 +12875,13 @@
         <v>76</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>107</v>
@@ -12948,10 +12951,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12974,13 +12977,13 @@
         <v>76</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13031,7 +13034,7 @@
         <v>76</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>74</v>
@@ -13048,10 +13051,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13077,13 +13080,13 @@
         <v>119</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13133,7 +13136,7 @@
         <v>76</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>74</v>
@@ -13150,10 +13153,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13176,19 +13179,19 @@
         <v>84</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>388</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>76</v>
@@ -13237,7 +13240,7 @@
         <v>76</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>74</v>
@@ -13254,10 +13257,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13280,19 +13283,19 @@
         <v>84</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>76</v>
@@ -13329,17 +13332,17 @@
         <v>76</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>74</v>
@@ -13348,7 +13351,7 @@
         <v>83</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>91</v>
@@ -13356,13 +13359,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>76</v>
@@ -13384,19 +13387,19 @@
         <v>84</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>76</v>
@@ -13445,7 +13448,7 @@
         <v>76</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>74</v>
@@ -13454,7 +13457,7 @@
         <v>83</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>91</v>
@@ -13462,10 +13465,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13562,10 +13565,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13664,13 +13667,13 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B107" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="B107" t="s" s="2">
-        <v>534</v>
-      </c>
       <c r="C107" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>103</v>
@@ -13692,16 +13695,16 @@
         <v>76</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -13768,10 +13771,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13794,19 +13797,19 @@
         <v>84</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>76</v>
@@ -13855,7 +13858,7 @@
         <v>76</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>74</v>
@@ -13872,10 +13875,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13972,10 +13975,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14074,13 +14077,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="B111" t="s" s="2">
-        <v>552</v>
-      </c>
       <c r="C111" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>103</v>
@@ -14102,16 +14105,16 @@
         <v>76</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14178,10 +14181,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14204,13 +14207,13 @@
         <v>76</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -14261,7 +14264,7 @@
         <v>76</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>74</v>
@@ -14278,10 +14281,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14307,22 +14310,22 @@
         <v>159</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>327</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q113" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="R113" t="s" s="2">
         <v>76</v>
@@ -14346,10 +14349,10 @@
         <v>225</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>76</v>
@@ -14367,7 +14370,7 @@
         <v>76</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>74</v>
@@ -14384,10 +14387,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14413,16 +14416,16 @@
         <v>98</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>327</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>76</v>
@@ -14471,7 +14474,7 @@
         <v>76</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>74</v>
@@ -14488,10 +14491,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14517,23 +14520,23 @@
         <v>125</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q115" s="2"/>
       <c r="R115" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S115" t="s" s="2">
         <v>76</v>
@@ -14575,7 +14578,7 @@
         <v>76</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>74</v>
@@ -14584,7 +14587,7 @@
         <v>83</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>91</v>
@@ -14592,10 +14595,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14621,16 +14624,16 @@
         <v>159</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>76</v>
@@ -14659,7 +14662,7 @@
       </c>
       <c r="Y116" s="2"/>
       <c r="Z116" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>76</v>
@@ -14677,7 +14680,7 @@
         <v>76</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>74</v>
@@ -14694,13 +14697,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>76</v>
@@ -14725,16 +14728,16 @@
         <v>282</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>76</v>
@@ -14763,7 +14766,7 @@
       </c>
       <c r="Y117" s="2"/>
       <c r="Z117" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>76</v>
@@ -14781,7 +14784,7 @@
         <v>76</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>74</v>
@@ -14790,7 +14793,7 @@
         <v>83</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>91</v>
@@ -14798,10 +14801,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14898,10 +14901,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15000,10 +15003,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15104,10 +15107,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15204,10 +15207,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15306,10 +15309,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15410,10 +15413,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15512,10 +15515,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15616,10 +15619,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15720,10 +15723,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15824,10 +15827,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15928,13 +15931,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>76</v>
@@ -15956,19 +15959,19 @@
         <v>84</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>76</v>
@@ -16017,7 +16020,7 @@
         <v>76</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>74</v>
@@ -16026,7 +16029,7 @@
         <v>83</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>91</v>
@@ -16034,13 +16037,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>76</v>
@@ -16062,19 +16065,19 @@
         <v>84</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>76</v>
@@ -16123,7 +16126,7 @@
         <v>76</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>74</v>
@@ -16132,7 +16135,7 @@
         <v>83</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>91</v>
@@ -16140,10 +16143,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16169,16 +16172,16 @@
         <v>282</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>76</v>
@@ -16207,7 +16210,7 @@
       </c>
       <c r="Y131" s="2"/>
       <c r="Z131" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>76</v>
@@ -16225,7 +16228,7 @@
         <v>76</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>74</v>
@@ -16234,7 +16237,7 @@
         <v>83</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>91</v>
@@ -16242,14 +16245,14 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -16271,16 +16274,16 @@
         <v>282</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>76</v>
@@ -16308,10 +16311,10 @@
         <v>141</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>76</v>
@@ -16329,7 +16332,7 @@
         <v>76</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>74</v>
@@ -16346,10 +16349,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16372,19 +16375,19 @@
         <v>76</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>76</v>
@@ -16433,7 +16436,7 @@
         <v>76</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>74</v>
@@ -16450,10 +16453,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16479,13 +16482,13 @@
         <v>282</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -16514,10 +16517,10 @@
         <v>149</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>76</v>
@@ -16535,7 +16538,7 @@
         <v>76</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>74</v>
@@ -16552,10 +16555,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16581,16 +16584,16 @@
         <v>282</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>76</v>
@@ -16619,7 +16622,7 @@
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>76</v>
@@ -16637,7 +16640,7 @@
         <v>76</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>74</v>
@@ -16654,10 +16657,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16754,10 +16757,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16856,10 +16859,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16960,10 +16963,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17060,10 +17063,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17162,10 +17165,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17266,10 +17269,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -17368,10 +17371,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17472,10 +17475,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17576,10 +17579,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17680,10 +17683,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17784,10 +17787,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17810,16 +17813,16 @@
         <v>76</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -17869,7 +17872,7 @@
         <v>76</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>74</v>
@@ -17886,10 +17889,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17986,10 +17989,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18088,10 +18091,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18117,13 +18120,13 @@
         <v>98</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -18173,7 +18176,7 @@
         <v>76</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>74</v>
@@ -18182,7 +18185,7 @@
         <v>83</v>
       </c>
       <c r="AI150" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AJ150" t="s" s="2">
         <v>91</v>
@@ -18190,10 +18193,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -18219,13 +18222,13 @@
         <v>125</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -18254,10 +18257,10 @@
         <v>141</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>76</v>
@@ -18275,7 +18278,7 @@
         <v>76</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>74</v>
@@ -18292,10 +18295,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -18321,13 +18324,13 @@
         <v>258</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -18377,7 +18380,7 @@
         <v>76</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>74</v>
@@ -18394,10 +18397,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -18423,13 +18426,13 @@
         <v>98</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -18479,7 +18482,7 @@
         <v>76</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>74</v>
@@ -18496,10 +18499,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -18522,16 +18525,16 @@
         <v>76</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -18581,7 +18584,7 @@
         <v>76</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>74</v>
@@ -18598,10 +18601,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -18698,10 +18701,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18800,10 +18803,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18829,13 +18832,13 @@
         <v>98</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -18885,7 +18888,7 @@
         <v>76</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>74</v>
@@ -18894,7 +18897,7 @@
         <v>83</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>91</v>
@@ -18902,10 +18905,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -18931,13 +18934,13 @@
         <v>125</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -18966,10 +18969,10 @@
         <v>141</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>76</v>
@@ -18987,7 +18990,7 @@
         <v>76</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>74</v>
@@ -19004,10 +19007,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -19033,13 +19036,13 @@
         <v>258</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -19089,7 +19092,7 @@
         <v>76</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>74</v>
@@ -19106,10 +19109,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -19135,13 +19138,13 @@
         <v>98</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -19191,7 +19194,7 @@
         <v>76</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>74</v>
@@ -19208,10 +19211,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -19234,19 +19237,19 @@
         <v>76</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>76</v>
@@ -19295,7 +19298,7 @@
         <v>76</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>74</v>
@@ -19307,15 +19310,15 @@
         <v>90</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19412,10 +19415,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -19514,14 +19517,14 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
@@ -19543,10 +19546,10 @@
         <v>104</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="N164" t="s" s="2">
         <v>107</v>
@@ -19601,7 +19604,7 @@
         <v>76</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>74</v>
@@ -19618,10 +19621,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -19644,16 +19647,16 @@
         <v>76</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -19703,7 +19706,7 @@
         <v>76</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>74</v>
@@ -19712,18 +19715,18 @@
         <v>83</v>
       </c>
       <c r="AI165" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -19746,16 +19749,16 @@
         <v>76</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -19805,27 +19808,27 @@
         <v>76</v>
       </c>
       <c r="AF166" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AG166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH166" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI166" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AJ166" t="s" s="2">
         <v>711</v>
-      </c>
-      <c r="AG166" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH166" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI166" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="AJ166" t="s" s="2">
-        <v>710</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19851,16 +19854,16 @@
         <v>282</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>76</v>
@@ -19888,10 +19891,10 @@
         <v>163</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>76</v>
@@ -19909,7 +19912,7 @@
         <v>76</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>74</v>
@@ -19926,10 +19929,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19955,16 +19958,16 @@
         <v>282</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>76</v>
@@ -19992,10 +19995,10 @@
         <v>149</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>76</v>
@@ -20013,7 +20016,7 @@
         <v>76</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>74</v>
@@ -20030,10 +20033,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -20056,19 +20059,19 @@
         <v>76</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>76</v>
@@ -20117,7 +20120,7 @@
         <v>76</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>74</v>
@@ -20129,15 +20132,15 @@
         <v>90</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -20163,10 +20166,10 @@
         <v>98</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N170" t="s" s="2">
         <v>327</v>
@@ -20219,7 +20222,7 @@
         <v>76</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>74</v>
@@ -20236,10 +20239,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -20262,16 +20265,16 @@
         <v>84</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -20321,7 +20324,7 @@
         <v>76</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>74</v>
@@ -20338,10 +20341,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -20364,16 +20367,16 @@
         <v>84</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -20423,7 +20426,7 @@
         <v>76</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>74</v>
@@ -20440,10 +20443,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -20466,19 +20469,19 @@
         <v>84</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>76</v>
@@ -20527,7 +20530,7 @@
         <v>76</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>74</v>
@@ -20544,10 +20547,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -20644,10 +20647,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -20746,14 +20749,14 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -20775,10 +20778,10 @@
         <v>104</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="N176" t="s" s="2">
         <v>107</v>
@@ -20833,7 +20836,7 @@
         <v>76</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>74</v>
@@ -20850,10 +20853,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20879,16 +20882,16 @@
         <v>282</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>76</v>
@@ -20916,10 +20919,10 @@
         <v>149</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>76</v>
@@ -20937,7 +20940,7 @@
         <v>76</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>83</v>
@@ -20954,10 +20957,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20980,19 +20983,19 @@
         <v>84</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>76</v>
@@ -21041,7 +21044,7 @@
         <v>76</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>74</v>
@@ -21058,10 +21061,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -21087,16 +21090,16 @@
         <v>282</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>76</v>
@@ -21124,10 +21127,10 @@
         <v>141</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>76</v>
@@ -21145,7 +21148,7 @@
         <v>76</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>74</v>
@@ -21154,7 +21157,7 @@
         <v>83</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>91</v>
@@ -21162,14 +21165,14 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
@@ -21191,16 +21194,16 @@
         <v>282</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>76</v>
@@ -21228,10 +21231,10 @@
         <v>141</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>76</v>
@@ -21249,7 +21252,7 @@
         <v>76</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>74</v>
@@ -21266,10 +21269,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -21295,16 +21298,16 @@
         <v>77</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>76</v>
@@ -21353,7 +21356,7 @@
         <v>76</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>74</v>

--- a/StructureDefinition-mii-pr-mikrobio-antigen-antikoerper-quantitativ.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-antigen-antikoerper-quantitativ.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:00:57+00:00</t>
+    <t>2026-09-10T16:03:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-antigen-antikoerper-quantitativ.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-antigen-antikoerper-quantitativ.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:03:25+00:00</t>
+    <t>2026-09-10T16:53:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-antigen-antikoerper-quantitativ.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-antigen-antikoerper-quantitativ.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:53:22+00:00</t>
+    <t>2026-09-10T17:52:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-antigen-antikoerper-quantitativ.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-antigen-antikoerper-quantitativ.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:52:15+00:00</t>
+    <t>2026-09-11T12:05:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-antigen-antikoerper-quantitativ.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-antigen-antikoerper-quantitativ.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:05:40+00:00</t>
+    <t>2026-09-12T16:32:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-antigen-antikoerper-quantitativ.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-antigen-antikoerper-quantitativ.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:32:25+00:00</t>
+    <t>2026-09-12T17:28:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-antigen-antikoerper-quantitativ.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-antigen-antikoerper-quantitativ.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:28:38+00:00</t>
+    <t>2026-09-12T20:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
